--- a/jpcore-r4/feature/BodySiteに関するTerminologyの見直し/StructureDefinition-jp-imagingstudy-radiology.xlsx
+++ b/jpcore-r4/feature/BodySiteに関するTerminologyの見直し/StructureDefinition-jp-imagingstudy-radiology.xlsx
@@ -1230,7 +1230,7 @@
     <t>コードは、列挙型またはコードリストで、どの部位の検査なのかを示す。フリーではなく、DICOM定義書の中で示される語句（コード）をデフォルトとするが、JJ1017Pの小部位コードの利用を許容する。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_EndoScopy_BodySite_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ImagingStudy_Radiology_BodySite_VS</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
